--- a/015_Lago_Titicaca/_raw_reportes_xlsx/IDConfig_65371_completo.xlsx
+++ b/015_Lago_Titicaca/_raw_reportes_xlsx/IDConfig_65371_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R274a87dc159243d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb1a4c8a5e2424c66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5780</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5856</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/015_Lago_Titicaca/_raw_reportes_xlsx/IDConfig_65371_completo.xlsx
+++ b/015_Lago_Titicaca/_raw_reportes_xlsx/IDConfig_65371_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb1a4c8a5e2424c66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R71f16e62bd0b467c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4155</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4113</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4133</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4156</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4230</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4767</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4633</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5090</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5070</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5070</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5611</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.6175</x:v>
+        <x:v>      8.6182</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,102 +1149,102 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      8.6378</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      8.6370</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>11/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.6540</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.6220</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.6300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.6320</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.6300</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.6370</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>05/08/2026</x:t>
         </x:is>
       </x:c>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.6621</x:v>
+        <x:v>      8.6611</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.6638</x:v>
+        <x:v>      8.6642</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.6790</x:v>
+        <x:v>      8.6789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7050</x:v>
+        <x:v>      8.7025</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7483</x:v>
+        <x:v>      8.7482</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7638</x:v>
+        <x:v>      8.7627</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7625</x:v>
+        <x:v>      8.7627</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7775</x:v>
+        <x:v>      8.7778</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7813</x:v>
+        <x:v>      8.7809</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7775</x:v>
+        <x:v>      8.7774</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7814</x:v>
+        <x:v>      8.7815</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7888</x:v>
+        <x:v>      8.7887</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7929</x:v>
+        <x:v>      8.7939</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7942</x:v>
+        <x:v>      8.7952</x:v>
       </x:c>
     </x:row>
     <x:row>
